--- a/ticvai/repos/ticvai-backend/project-bible/handoff/TICVAI_Readiness_Questions.xlsx
+++ b/ticvai/repos/ticvai-backend/project-bible/handoff/TICVAI_Readiness_Questions.xlsx
@@ -16,8 +16,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Summary'!$A$1:$G$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Make or break'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Decided by us'!$A$1:$C$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Our work'!$A$1:$E$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Decided by us'!$A$1:$C$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Our work'!$A$1:$E$116</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wireframes'!$A$1:$F$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -529,7 +529,7 @@
         <v>77</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>0</v>
@@ -645,7 +645,7 @@
         <v>11</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>0</v>
@@ -674,7 +674,7 @@
         <v>1186</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1303</v>
+        <v>1362</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>3</v>
@@ -703,7 +703,7 @@
         <v>676</v>
       </c>
       <c r="D9" s="2" t="n">
-        <v>547</v>
+        <v>583</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1</v>
@@ -732,7 +732,7 @@
         <v>51</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0</v>
@@ -761,17 +761,17 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4 screens to specify; wireframes: 8 to verify</t>
+          <t>1 screens to specify; wireframes: 8 to verify</t>
         </is>
       </c>
     </row>
@@ -790,7 +790,7 @@
         <v>28</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0</v>
@@ -819,7 +819,7 @@
         <v>100</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>10</v>
       </c>
       <c r="D15" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>0</v>
@@ -906,7 +906,7 @@
         <v>69</v>
       </c>
       <c r="D16" s="2" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1477,8 +1477,38 @@
         <v>40</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Requirements re-traced against the current contracts (29 September)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>handoff/traceability.json</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AI system design questions and trade-offs (29 September)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>docs/architecture/ai-system-design.md, section 8 (draft, final read pending)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C5"/>
+  <autoFilter ref="A1:C7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1489,7 +1519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1824,30 +1854,30 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>P02</t>
+          <t>Requirements</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>screen names no operation</t>
+          <t>not covered or partly covered</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>GST-043 Arabic / RTL Experience</t>
+          <t>67 requirements: 5 not covered, 62 partly covered. Each is listed in TICVAI - Build Readiness.xlsx (sheet Missing, and its application's sheet)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Specify from its pack</t>
+          <t>Each has a contract-backlog entry naming the operation that would serve it</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>P05</t>
+          <t>P02</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1857,7 +1887,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>KSK-001 Attract Loop</t>
+          <t>GST-043 Arabic / RTL Experience</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr"/>
@@ -1880,7 +1910,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>KSK-014 Out of service</t>
+          <t>KSK-001 Attract Loop</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr"/>
@@ -1893,7 +1923,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>P06</t>
+          <t>P05</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1903,7 +1933,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EMP-044 Accessibility</t>
+          <t>KSK-014 Out of service</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr"/>
@@ -1926,7 +1956,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EMP-045 Arabic / RTL</t>
+          <t>EMP-044 Accessibility</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr"/>
@@ -1939,7 +1969,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>P08</t>
+          <t>P06</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1949,7 +1979,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BO-919 AI Event Resource Forecasting</t>
+          <t>EMP-045 Arabic / RTL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr"/>
@@ -1972,13 +2002,13 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>BO-925 AI Staff Recommendation &amp; Workforce Matching</t>
+          <t>BO-919 AI Event Resource Forecasting</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr"/>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Specify from its pack</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -1995,13 +2025,13 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>BO-926 Resource Demand Forecasting</t>
+          <t>BO-925 AI Staff Recommendation &amp; Workforce Matching</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Specify from its pack</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2048,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>BO-927 AI Staffing Requirement Forecast</t>
+          <t>BO-926 Resource Demand Forecasting</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr"/>
@@ -2041,13 +2071,13 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>BO-928 AI Conflict Resolution Assistant</t>
+          <t>BO-927 AI Staffing Requirement Forecast</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Specify from its pack</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2064,13 +2094,13 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>BO-929 Automatic Schedule Optimization</t>
+          <t>BO-928 AI Conflict Resolution Assistant</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Specify from its pack</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2117,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>BO-931 Operational Scenario Simulator &amp; Digital Twin</t>
+          <t>BO-929 Automatic Schedule Optimization</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr"/>
@@ -2110,7 +2140,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>BO-932 Conversational AI Resource Copilot</t>
+          <t>BO-931 Operational Scenario Simulator &amp; Digital Twin</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -2123,7 +2153,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>P09</t>
+          <t>P08</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2133,13 +2163,13 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>ADM-469 AI Configuration Home &amp; Start</t>
+          <t>BO-932 Conversational AI Resource Copilot</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2156,13 +2186,13 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>ADM-470 Setup Type &amp; Business Intent Discovery</t>
+          <t>ADM-469 AI Configuration Home &amp; Start</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr"/>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2179,13 +2209,13 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>ADM-471 Venue &amp; Business Model Discovery</t>
+          <t>ADM-470 Setup Type &amp; Business Intent Discovery</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2202,13 +2232,13 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>ADM-472 Guided Question &amp; Answer Workspace</t>
+          <t>ADM-471 Venue &amp; Business Model Discovery</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2225,13 +2255,13 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>ADM-473 Product &amp; Admission Model Discovery</t>
+          <t>ADM-472 Guided Question &amp; Answer Workspace</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2248,13 +2278,13 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>ADM-474 Operational Requirement Discovery</t>
+          <t>ADM-473 Product &amp; Admission Model Discovery</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2271,13 +2301,13 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>ADM-475 Commercial Requirement Discovery</t>
+          <t>ADM-474 Operational Requirement Discovery</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2294,13 +2324,13 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>ADM-476 Required, Recommended &amp; Optional Decisions</t>
+          <t>ADM-475 Commercial Requirement Discovery</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2317,13 +2347,13 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>ADM-477 Missing Information &amp; Clarification Center</t>
+          <t>ADM-476 Required, Recommended &amp; Optional Decisions</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr"/>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2340,13 +2370,13 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>ADM-478 Configuration Blueprint &amp; Dependency Map</t>
+          <t>ADM-477 Missing Information &amp; Clarification Center</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2363,13 +2393,13 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>ADM-479 AI Configuration Build Command Center</t>
+          <t>ADM-478 Configuration Blueprint &amp; Dependency Map</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2386,13 +2416,13 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>ADM-480 Venue &amp; Organization Configuration</t>
+          <t>ADM-479 AI Configuration Build Command Center</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2409,13 +2439,13 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>ADM-481 Product Configuration Assistant</t>
+          <t>ADM-480 Venue &amp; Organization Configuration</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2432,13 +2462,13 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>ADM-482 Schedule, Capacity &amp; Availability Configuration</t>
+          <t>ADM-481 Product Configuration Assistant</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr"/>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2455,13 +2485,13 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>ADM-484 Promotion, Bundle &amp; Upsell Configuration</t>
+          <t>ADM-482 Schedule, Capacity &amp; Availability Configuration</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2478,13 +2508,13 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>ADM-485 Seating, Access &amp; Operational Configuration</t>
+          <t>ADM-484 Promotion, Bundle &amp; Upsell Configuration</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2501,13 +2531,13 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>ADM-486 Channel, Media &amp; Fulfillment Configuration</t>
+          <t>ADM-485 Seating, Access &amp; Operational Configuration</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2524,13 +2554,13 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>ADM-487 Cross-Module Conflict &amp; Dependency Validation</t>
+          <t>ADM-486 Channel, Media &amp; Fulfillment Configuration</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2547,13 +2577,13 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>ADM-488 Configuration Preview &amp; Impact Analysis</t>
+          <t>ADM-487 Cross-Module Conflict &amp; Dependency Validation</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2570,13 +2600,13 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>ADM-489 AI Configuration Readiness Center</t>
+          <t>ADM-488 Configuration Preview &amp; Impact Analysis</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2593,13 +2623,13 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>ADM-490 Configuration Validation Results</t>
+          <t>ADM-489 AI Configuration Readiness Center</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2616,13 +2646,13 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>ADM-491 AI Recommendations &amp; Best-Practice Review</t>
+          <t>ADM-490 Configuration Validation Results</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2639,13 +2669,13 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>ADM-493 AI Configuration Execution Center</t>
+          <t>ADM-491 AI Recommendations &amp; Best-Practice Review</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2662,13 +2692,13 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>ADM-494 Execution Progress &amp; Dependency Monitor</t>
+          <t>ADM-493 AI Configuration Execution Center</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2685,13 +2715,13 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>ADM-495 Configuration Results &amp; Object Mapping</t>
+          <t>ADM-494 Execution Progress &amp; Dependency Monitor</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2708,13 +2738,13 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>ADM-496 Configuration Change &amp; Modification Assistant</t>
+          <t>ADM-495 Configuration Results &amp; Object Mapping</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2731,13 +2761,13 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ADM-497 Configuration History, Versions &amp; Rollback</t>
+          <t>ADM-496 Configuration Change &amp; Modification Assistant</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2754,13 +2784,13 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>ADM-498 AI Configuration Audit &amp; Governance</t>
+          <t>ADM-497 Configuration History, Versions &amp; Rollback</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2777,13 +2807,13 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>ADM-499 Forecasting Command Center</t>
+          <t>ADM-498 AI Configuration Audit &amp; Governance</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2800,13 +2830,13 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ADM-500 Forecast Configuration &amp; Forecasting Strategy</t>
+          <t>ADM-499 Forecasting Command Center</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2823,13 +2853,13 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ADM-501 Forecast Data &amp; Signal Configuration</t>
+          <t>ADM-500 Forecast Configuration &amp; Forecasting Strategy</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2846,13 +2876,13 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>ADM-502 Attendance &amp; Visitation Forecast</t>
+          <t>ADM-501 Forecast Data &amp; Signal Configuration</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2869,13 +2899,13 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ADM-503 Ticket, Product &amp; Timeslot Demand Forecast</t>
+          <t>ADM-502 Attendance &amp; Visitation Forecast</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2892,13 +2922,13 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ADM-504 Channel &amp; Booking Pace Forecast</t>
+          <t>ADM-503 Ticket, Product &amp; Timeslot Demand Forecast</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2915,13 +2945,13 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ADM-505 Revenue &amp; Commercial Forecast</t>
+          <t>ADM-504 Channel &amp; Booking Pace Forecast</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2938,13 +2968,13 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ADM-506 Forecast Drivers, Confidence &amp; Explainability</t>
+          <t>ADM-505 Revenue &amp; Commercial Forecast</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2961,13 +2991,13 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ADM-507 Forecast Scenario &amp; What-If Simulator</t>
+          <t>ADM-506 Forecast Drivers, Confidence &amp; Explainability</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -2984,13 +3014,13 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ADM-508 Forecast Accuracy, Review &amp; Publication Center</t>
+          <t>ADM-507 Forecast Scenario &amp; What-If Simulator</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3007,13 +3037,13 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ADM-509 Operational Forecasting Command Center</t>
+          <t>ADM-508 Forecast Accuracy, Review &amp; Publication Center</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3030,13 +3060,13 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ADM-510 Capacity &amp; Occupancy Forecast</t>
+          <t>ADM-509 Operational Forecasting Command Center</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3053,13 +3083,13 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ADM-511 Attraction Utilization &amp; Queue Forecast</t>
+          <t>ADM-510 Capacity &amp; Occupancy Forecast</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3076,13 +3106,13 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>ADM-512 Entry, Access &amp; Guest Flow Forecast</t>
+          <t>ADM-511 Attraction Utilization &amp; Queue Forecast</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3099,13 +3129,13 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ADM-513 Workforce Demand &amp; Staffing Forecast</t>
+          <t>ADM-512 Entry, Access &amp; Guest Flow Forecast</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3122,13 +3152,13 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>ADM-514 POS, Kiosk &amp; Frontline Service Forecast</t>
+          <t>ADM-513 Workforce Demand &amp; Staffing Forecast</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3145,13 +3175,13 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>ADM-515 F&amp;B, Retail &amp; Inventory Demand Forecast</t>
+          <t>ADM-514 POS, Kiosk &amp; Frontline Service Forecast</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3168,13 +3198,13 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ADM-516 Resource, Equipment &amp; Facility Requirement Forecast</t>
+          <t>ADM-515 F&amp;B, Retail &amp; Inventory Demand Forecast</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3191,13 +3221,13 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ADM-517 Operational Scenario &amp; Readiness Simulator</t>
+          <t>ADM-516 Resource, Equipment &amp; Facility Requirement Forecast</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3214,13 +3244,13 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ADM-518 Operational Forecast Review, Recommendations &amp; Handover</t>
+          <t>ADM-517 Operational Scenario &amp; Readiness Simulator</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3237,13 +3267,13 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>ADM-519 AI Governance Command Center</t>
+          <t>ADM-518 Operational Forecast Review, Recommendations &amp; Handover</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3260,13 +3290,13 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>ADM-520 AI Capability Registry &amp; Ownership</t>
+          <t>ADM-519 AI Governance Command Center</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3283,13 +3313,13 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>ADM-521 AI Risk Classification &amp; Assessment</t>
+          <t>ADM-520 AI Capability Registry &amp; Ownership</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3306,13 +3336,13 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>ADM-522 AI Autonomy Level Configuration</t>
+          <t>ADM-521 AI Risk Classification &amp; Assessment</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3329,13 +3359,13 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>ADM-523 AI Action &amp; Permission Policy Builder</t>
+          <t>ADM-522 AI Autonomy Level Configuration</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3352,13 +3382,13 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ADM-524 AI Data Access &amp; Usage Policy</t>
+          <t>ADM-523 AI Action &amp; Permission Policy Builder</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3375,13 +3405,13 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ADM-525 Environment, Tenant &amp; Scope Governance</t>
+          <t>ADM-524 AI Data Access &amp; Usage Policy</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3398,13 +3428,13 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ADM-526 AI Policy Conflict, Exception &amp; Override Management</t>
+          <t>ADM-525 Environment, Tenant &amp; Scope Governance</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3421,13 +3451,13 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ADM-527 AI Policy Testing &amp; Governance Simulation</t>
+          <t>ADM-526 AI Policy Conflict, Exception &amp; Override Management</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3444,13 +3474,13 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>ADM-528 AI Governance Policy Publication &amp; Effective Policy Map</t>
+          <t>ADM-527 AI Policy Testing &amp; Governance Simulation</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3467,13 +3497,13 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>ADM-529 AI Human Oversight Command Center</t>
+          <t>ADM-528 AI Governance Policy Publication &amp; Effective Policy Map</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3490,13 +3520,13 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ADM-530 AI Approval Requirement &amp; Routing Configuration</t>
+          <t>ADM-529 AI Human Oversight Command Center</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3513,13 +3543,13 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ADM-531 AI Approval Review Workspace</t>
+          <t>ADM-530 AI Approval Requirement &amp; Routing Configuration</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3536,13 +3566,13 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>ADM-532 Conditional Approval &amp; Approval Conditions</t>
+          <t>ADM-531 AI Approval Review Workspace</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3559,13 +3589,13 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ADM-533 Human Review, Challenge &amp; AI Clarification Workspace</t>
+          <t>ADM-532 Conditional Approval &amp; Approval Conditions</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3582,13 +3612,13 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>ADM-534 Escalation, Delegation &amp; Approval SLA Management</t>
+          <t>ADM-533 Human Review, Challenge &amp; AI Clarification Workspace</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3605,13 +3635,13 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ADM-535 Live AI Execution Oversight &amp; Human Intervention</t>
+          <t>ADM-534 Escalation, Delegation &amp; Approval SLA Management</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3628,13 +3658,13 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ADM-536 Human Override &amp; Manual Control Center</t>
+          <t>ADM-535 Live AI Execution Oversight &amp; Human Intervention</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3681,13 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ADM-537 Approval &amp; Intervention History / Decision Timeline</t>
+          <t>ADM-536 Human Override &amp; Manual Control Center</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3674,13 +3704,13 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ADM-538 Human Oversight Workflow Simulator &amp; Readiness Center</t>
+          <t>ADM-537 Approval &amp; Intervention History / Decision Timeline</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3697,13 +3727,13 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ADM-539 AI Explainability &amp; Audit Command Center</t>
+          <t>ADM-538 Human Oversight Workflow Simulator &amp; Readiness Center</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3720,13 +3750,13 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ADM-540 AI Decision Explorer &amp; Search</t>
+          <t>ADM-539 AI Explainability &amp; Audit Command Center</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3743,13 +3773,13 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ADM-541 AI Decision Explanation Workspace</t>
+          <t>ADM-540 AI Decision Explorer &amp; Search</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3766,13 +3796,13 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>ADM-542 Data, Feature &amp; Evidence Provenance</t>
+          <t>ADM-541 AI Decision Explanation Workspace</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3789,13 +3819,13 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ADM-543 Candidate, Rule &amp; Decision Path Trace</t>
+          <t>ADM-542 Data, Feature &amp; Evidence Provenance</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3812,13 +3842,13 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ADM-544 Model, Provider &amp; AI Runtime Trace</t>
+          <t>ADM-543 Candidate, Rule &amp; Decision Path Trace</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3835,13 +3865,13 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>ADM-545 Governance, Approval &amp; Human Decision Trace</t>
+          <t>ADM-544 Model, Provider &amp; AI Runtime Trace</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3858,13 +3888,13 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>ADM-546 Execution &amp; Business Outcome Trace</t>
+          <t>ADM-545 Governance, Approval &amp; Human Decision Trace</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3881,13 +3911,13 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ADM-547 AI Audit Record &amp; Evidence Package</t>
+          <t>ADM-546 Execution &amp; Business Outcome Trace</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3904,13 +3934,13 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ADM-548 AI Trace Investigation &amp; Replay Simulator</t>
+          <t>ADM-547 AI Audit Record &amp; Evidence Package</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3927,13 +3957,13 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ADM-550 AI Risk Register &amp; Risk Exposure Management</t>
+          <t>ADM-548 AI Trace Investigation &amp; Replay Simulator</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3950,13 +3980,13 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>ADM-551 AI Governance Control Library &amp; Control Effectiveness</t>
+          <t>ADM-550 AI Risk Register &amp; Risk Exposure Management</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3973,13 +4003,13 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ADM-552 AI Policy Compliance &amp; Violation Monitoring</t>
+          <t>ADM-551 AI Governance Control Library &amp; Control Effectiveness</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -3996,13 +4026,13 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>ADM-553 AI Data, Privacy &amp; Usage Compliance Monitoring</t>
+          <t>ADM-552 AI Policy Compliance &amp; Violation Monitoring</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -4019,13 +4049,13 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>ADM-554 AI Quality, Behavior &amp; Governance Drift Monitoring</t>
+          <t>ADM-553 AI Data, Privacy &amp; Usage Compliance Monitoring</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -4042,13 +4072,13 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>ADM-555 AI Governance Alert &amp; Detection Center</t>
+          <t>ADM-554 AI Quality, Behavior &amp; Governance Drift Monitoring</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -4065,13 +4095,13 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>ADM-556 AI Incident &amp; Remediation Management</t>
+          <t>ADM-555 AI Governance Alert &amp; Detection Center</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -4088,13 +4118,13 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ADM-557 AI Compliance, Assurance &amp; Governance Reporting</t>
+          <t>ADM-556 AI Incident &amp; Remediation Management</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -4111,13 +4141,13 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>ADM-558 AI Governance Review, Action Plan &amp; Continuous Improvement</t>
+          <t>ADM-557 AI Compliance, Assurance &amp; Governance Reporting</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -4134,20 +4164,20 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ADM-618 Refund Simulator, Risk Analysis &amp; AI Advisor\t126</t>
+          <t>ADM-558 AI Governance Review, Action Plan &amp; Continuous Improvement</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Waits on the AI design review</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P09</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -4157,13 +4187,13 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ACC-001 Landing / Programme Overview</t>
+          <t>ADM-618 Refund Simulator, Risk Analysis &amp; AI Advisor\t126</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Specify from its pack</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4210,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ACC-002 Registration Form</t>
+          <t>ACC-001 Landing / Programme Overview</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr"/>
@@ -4193,7 +4223,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>P11</t>
+          <t>P16</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -4203,64 +4233,18 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>ACC-003 Application Review &amp; Submit</t>
+          <t>ANL-060 AI Analytics Governance &amp; Model Control</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Specify from its pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>P11</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>screen names no operation</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>ACC-004 Application Status Tracking</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr"/>
-      <c r="E117" s="2" t="inlineStr">
-        <is>
-          <t>Specify from its pack</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>screen names no operation</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>ANL-060 AI Analytics Governance &amp; Model Control</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr"/>
-      <c r="E118" s="2" t="inlineStr">
-        <is>
-          <t>Specify from its pack</t>
+          <t>Waits on the AI operations in ai.yaml (design decided 29 September)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E118"/>
+  <autoFilter ref="A1:E116"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
